--- a/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/MANGUERA LAVARROPAS DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/MANGUERA LAVARROPAS DISMAY.xlsx
@@ -722,13 +722,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45113.64987684997</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45266</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -768,19 +764,10 @@
     <row r="11" ht="41.25" customHeight="1" s="24">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
+          <t>    </t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="31.5" customHeight="1" s="24">
       <c r="A21" s="18" t="inlineStr">
         <is>
@@ -825,7 +812,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>660</v>
+        <v>693</v>
       </c>
       <c r="E23" s="22" t="n"/>
     </row>
@@ -846,7 +833,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>747</v>
+        <v>785</v>
       </c>
       <c r="E24" s="22" t="n"/>
     </row>
@@ -867,7 +854,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>733</v>
+        <v>954</v>
       </c>
       <c r="E25" s="22" t="n"/>
     </row>
@@ -888,7 +875,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1016</v>
+        <v>1066</v>
       </c>
       <c r="E26" s="22" t="n"/>
     </row>
@@ -909,7 +896,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>1140</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="24">
@@ -918,7 +905,6 @@
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="22" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="15.75" customHeight="1" s="24">
       <c r="A30" s="8" t="inlineStr">
         <is>
@@ -975,7 +961,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>424</v>
+        <v>577</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="24">
@@ -995,10 +981,9 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="36"/>
+        <v>725.1</v>
+      </c>
+    </row>
     <row r="37" ht="15.75" customHeight="1" s="24">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -1013,7 +998,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="15.75" customHeight="1" s="24">
       <c r="A40" s="16" t="inlineStr">
         <is>
